--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251208_201531.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
